--- a/12605212.xlsx
+++ b/12605212.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>I am unwell with a fever today.</t>
+  </si>
+  <si>
+    <t>I am unwell with fever and cold.</t>
+  </si>
+  <si>
+    <t>I am very tired .</t>
   </si>
 </sst>
 </file>
@@ -2220,48 +2226,92 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="A30" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
       <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>45</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="A31" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
       <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>50</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
